--- a/manuscript_submission_snapshot/additional_files/additional_file_3_lfo_functional_change_associations.xlsx
+++ b/manuscript_submission_snapshot/additional_files/additional_file_3_lfo_functional_change_associations.xlsx
@@ -7,14 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="decoupled_comparison" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="leakage_audit" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="strict_core_lfo" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lfo_sensitivity" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="class_risks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="auc_bootstrap" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="heterogeneity" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sheet_index" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="decoupled_comparison" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="leakage_audit" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="strict_core_lfo" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lfo_sensitivity" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="class_risks" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="auc_bootstrap" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="heterogeneity" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -36,12 +37,17 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -56,9 +62,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,6 +431,132 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="57" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>README</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Workbook overview.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>decoupled_comparison</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LFO profile versus continuous-score comparator outputs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>leakage_audit</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Functional endpoint leakage and LFO design audit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>strict_core_lfo</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Strict-core LFO functional-change association table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>lfo_sensitivity</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SHARE/KLoSA sensitivity rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>class_risks</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Class-level functional-change risks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>auc_bootstrap</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>AUC bootstrap intervals and deltas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>heterogeneity</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Cross-cohort functional-change heterogeneity summaries.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -493,7 +626,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
@@ -652,7 +784,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2518,7 +2650,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3483,7 +3615,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4107,7 +4239,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4497,7 +4629,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6225,7 +6357,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6579,7 +6711,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
